--- a/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
+++ b/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
@@ -14313,10 +14313,10 @@
         </is>
       </c>
       <c r="H221" s="5" t="n">
-        <v>1837500018651000</v>
+        <v>18651000</v>
       </c>
       <c r="I221" s="5" t="n">
-        <v>3365384649544</v>
+        <v>34160</v>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
@@ -14324,10 +14324,10 @@
         </is>
       </c>
       <c r="K221" s="5" t="n">
-        <v>1697827048483200</v>
+        <v>17233524</v>
       </c>
       <c r="L221" s="5" t="n">
-        <v>3109573348870</v>
+        <v>31563</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
@@ -15615,10 +15615,10 @@
         </is>
       </c>
       <c r="H242" s="5" t="n">
-        <v>2796300028662000</v>
+        <v>28662000</v>
       </c>
       <c r="I242" s="5" t="n">
-        <v>3145444351701</v>
+        <v>32241</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
@@ -15626,10 +15626,10 @@
         </is>
       </c>
       <c r="K242" s="5" t="n">
-        <v>2583746272733300</v>
+        <v>26483688</v>
       </c>
       <c r="L242" s="5" t="n">
-        <v>2906351262917</v>
+        <v>29790</v>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
@@ -15987,10 +15987,10 @@
         </is>
       </c>
       <c r="H248" s="5" t="n">
-        <v>1803600018307000</v>
+        <v>18307000</v>
       </c>
       <c r="I248" s="5" t="n">
-        <v>3303296736826</v>
+        <v>33529</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
@@ -15998,10 +15998,10 @@
         </is>
       </c>
       <c r="K248" s="5" t="n">
-        <v>1666503871915300</v>
+        <v>16915668</v>
       </c>
       <c r="L248" s="5" t="n">
-        <v>3052204893618</v>
+        <v>30981</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
@@ -16173,10 +16173,10 @@
         </is>
       </c>
       <c r="H251" s="5" t="n">
-        <v>2796000028659000</v>
+        <v>28659000</v>
       </c>
       <c r="I251" s="5" t="n">
-        <v>3145106893880</v>
+        <v>32237</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
@@ -16184,10 +16184,10 @@
         </is>
       </c>
       <c r="K251" s="5" t="n">
-        <v>2583469076480500</v>
+        <v>26480916</v>
       </c>
       <c r="L251" s="5" t="n">
-        <v>2906039456109</v>
+        <v>29787</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
@@ -16545,10 +16545,10 @@
         </is>
       </c>
       <c r="H257" s="5" t="n">
-        <v>1797900018249000</v>
+        <v>18249000</v>
       </c>
       <c r="I257" s="5" t="n">
-        <v>3292857176280</v>
+        <v>33423</v>
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
@@ -16556,10 +16556,10 @@
         </is>
       </c>
       <c r="K257" s="5" t="n">
-        <v>1661237143111700</v>
+        <v>16862076</v>
       </c>
       <c r="L257" s="5" t="n">
-        <v>3042558870168</v>
+        <v>30883</v>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
@@ -32663,8 +32663,8 @@
       <c r="B31" s="24" t="inlineStr">
         <is>
           <t>A | 889呎 (3房)
-$279630002866万
-$3,145,444,351,701/呎
+万
+,241/呎
 (暂停销售)</t>
         </is>
       </c>

--- a/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
+++ b/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
@@ -847,7 +847,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -909,7 +909,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2022-09-28</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2021-06-06</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2021-07-20</t>
+          <t>2021-07-21</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
+          <t>2021-08-05</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
+          <t>2021-07-30</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2021-06-06</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2021-06-18</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2021-06-06</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
+          <t>2021-07-26</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
+          <t>2021-08-05</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11395,7 +11395,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11519,7 +11519,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12821,7 +12821,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13007,7 +13007,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13627,7 +13627,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13689,7 +13689,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14185,7 +14185,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14313,10 +14313,10 @@
         </is>
       </c>
       <c r="H221" s="5" t="n">
-        <v>18651000</v>
+        <v>1837500018651000</v>
       </c>
       <c r="I221" s="5" t="n">
-        <v>34160</v>
+        <v>3365384649544</v>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
@@ -14324,10 +14324,10 @@
         </is>
       </c>
       <c r="K221" s="5" t="n">
-        <v>17233524</v>
+        <v>1697827048483200</v>
       </c>
       <c r="L221" s="5" t="n">
-        <v>31563</v>
+        <v>3109573348870</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14805,7 +14805,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024-01-02</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
+          <t>2021-08-06</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15239,7 +15239,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15363,7 +15363,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15425,7 +15425,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15615,10 +15615,10 @@
         </is>
       </c>
       <c r="H242" s="5" t="n">
-        <v>28662000</v>
+        <v>2796300028662000</v>
       </c>
       <c r="I242" s="5" t="n">
-        <v>32241</v>
+        <v>3145444351701</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
@@ -15626,10 +15626,10 @@
         </is>
       </c>
       <c r="K242" s="5" t="n">
-        <v>26483688</v>
+        <v>2583746272733300</v>
       </c>
       <c r="L242" s="5" t="n">
-        <v>29790</v>
+        <v>2906351262917</v>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -15987,10 +15987,10 @@
         </is>
       </c>
       <c r="H248" s="5" t="n">
-        <v>18307000</v>
+        <v>1803600018307000</v>
       </c>
       <c r="I248" s="5" t="n">
-        <v>33529</v>
+        <v>3303296736826</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
@@ -15998,10 +15998,10 @@
         </is>
       </c>
       <c r="K248" s="5" t="n">
-        <v>16915668</v>
+        <v>1666503871915300</v>
       </c>
       <c r="L248" s="5" t="n">
-        <v>30981</v>
+        <v>3052204893618</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
@@ -16173,10 +16173,10 @@
         </is>
       </c>
       <c r="H251" s="5" t="n">
-        <v>28659000</v>
+        <v>2796000028659000</v>
       </c>
       <c r="I251" s="5" t="n">
-        <v>32237</v>
+        <v>3145106893880</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
@@ -16184,10 +16184,10 @@
         </is>
       </c>
       <c r="K251" s="5" t="n">
-        <v>26480916</v>
+        <v>2583469076480500</v>
       </c>
       <c r="L251" s="5" t="n">
-        <v>29787</v>
+        <v>2906039456109</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16355,7 +16355,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16417,7 +16417,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16479,7 +16479,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16545,10 +16545,10 @@
         </is>
       </c>
       <c r="H257" s="5" t="n">
-        <v>18249000</v>
+        <v>1797900018249000</v>
       </c>
       <c r="I257" s="5" t="n">
-        <v>33423</v>
+        <v>3292857176280</v>
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
@@ -16556,10 +16556,10 @@
         </is>
       </c>
       <c r="K257" s="5" t="n">
-        <v>16862076</v>
+        <v>1661237143111700</v>
       </c>
       <c r="L257" s="5" t="n">
-        <v>30883</v>
+        <v>3042558870168</v>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2021-06-18</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -16975,7 +16975,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17037,7 +17037,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17347,7 +17347,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17409,7 +17409,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2021-08-02</t>
+          <t>2021-08-03</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17471,7 +17471,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2021-07-04</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17533,7 +17533,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17595,7 +17595,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17905,7 +17905,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -17967,7 +17967,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2021-08-03</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18029,7 +18029,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18091,7 +18091,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18463,7 +18463,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18525,7 +18525,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2021-08-30</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18587,7 +18587,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18649,7 +18649,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -19021,7 +19021,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19145,7 +19145,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19207,7 +19207,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19269,7 +19269,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19331,7 +19331,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2021-08-03</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2021-07-14</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19517,7 +19517,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -19579,7 +19579,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -19765,7 +19765,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2021-06-14</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -19827,7 +19827,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2021-08-02</t>
+          <t>2021-08-03</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -19889,7 +19889,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -20013,7 +20013,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20075,7 +20075,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
+          <t>2021-07-23</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20137,7 +20137,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2021-06-06</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20261,7 +20261,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20323,7 +20323,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20385,7 +20385,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20447,7 +20447,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -20509,7 +20509,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -20571,7 +20571,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2021-07-19</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -20633,7 +20633,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -20695,7 +20695,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -20819,7 +20819,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2021-08-19</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -20881,7 +20881,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
+          <t>2021-08-06</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -20943,7 +20943,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
+          <t>2021-07-16</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -21005,7 +21005,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21067,7 +21067,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2021-07-20</t>
+          <t>2021-07-21</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21129,7 +21129,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2021-06-06</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21253,7 +21253,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21315,7 +21315,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21377,7 +21377,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -21439,7 +21439,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
+          <t>2021-07-16</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -21563,7 +21563,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2021-07-10</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -21625,7 +21625,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -21687,7 +21687,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2021-05-28</t>
+          <t>2021-05-29</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -21749,7 +21749,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -21811,7 +21811,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -21873,7 +21873,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -21935,7 +21935,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2021-07-04</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -21997,7 +21997,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22059,7 +22059,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
+          <t>2021-07-16</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22183,7 +22183,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22307,7 +22307,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22369,7 +22369,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -22431,7 +22431,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2021-07-19</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -22493,7 +22493,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -22555,7 +22555,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -22617,7 +22617,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -22679,7 +22679,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -22741,7 +22741,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2021-06-18</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -22803,7 +22803,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -22865,7 +22865,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -22927,7 +22927,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2021-07-19</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -22989,7 +22989,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23051,7 +23051,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23113,7 +23113,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -23175,7 +23175,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -23237,7 +23237,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -23299,7 +23299,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -23361,7 +23361,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -23423,7 +23423,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -23547,7 +23547,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2021-06-18</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -23609,7 +23609,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -23671,7 +23671,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -23733,7 +23733,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
+          <t>2021-07-23</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2021-07-14</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -23857,7 +23857,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -23919,7 +23919,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -23981,7 +23981,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24043,7 +24043,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2021-06-18</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -24105,7 +24105,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -24167,7 +24167,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -24229,7 +24229,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
+          <t>2021-07-16</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -24291,7 +24291,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -24353,7 +24353,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -24415,7 +24415,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2021-07-20</t>
+          <t>2021-07-21</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -24477,7 +24477,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2021-07-04</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -24539,7 +24539,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2021-07-04</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -24601,7 +24601,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -24663,7 +24663,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -24725,7 +24725,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -24849,7 +24849,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
+          <t>2021-08-26</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -24911,7 +24911,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2021-06-19</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -24973,7 +24973,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -25035,7 +25035,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -25097,7 +25097,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -25159,7 +25159,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -25221,7 +25221,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -25283,7 +25283,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -25345,7 +25345,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -25407,7 +25407,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
+          <t>2021-07-23</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -25469,7 +25469,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -25531,7 +25531,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -25593,7 +25593,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -25655,7 +25655,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2021-07-02</t>
+          <t>2021-07-03</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -25717,7 +25717,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -25779,7 +25779,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -25841,7 +25841,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H407" s="5" t="n">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2021-07-20</t>
+          <t>2021-07-21</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -25965,7 +25965,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -26027,7 +26027,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -26151,7 +26151,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2021-07-19</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -26213,7 +26213,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -26275,7 +26275,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
@@ -26337,7 +26337,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
+          <t>2021-05-20</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -26399,7 +26399,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
+          <t>2021-07-16</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
@@ -26461,7 +26461,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="H417" s="5" t="n">
@@ -26523,7 +26523,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -26585,7 +26585,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -26647,7 +26647,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
@@ -26709,7 +26709,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -26771,7 +26771,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -26833,7 +26833,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -26895,7 +26895,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2021-08-12</t>
         </is>
       </c>
       <c r="H424" s="5" t="n">
@@ -26957,7 +26957,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
+          <t>2021-08-05</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -27019,7 +27019,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -27081,7 +27081,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
+          <t>2021-07-16</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
@@ -27143,7 +27143,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -27205,7 +27205,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -27329,7 +27329,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -27391,7 +27391,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -27453,7 +27453,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -27515,7 +27515,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H434" s="5" t="n">
@@ -27577,7 +27577,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
@@ -27639,7 +27639,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -27701,7 +27701,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H437" s="5" t="n">
@@ -27763,7 +27763,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2021-07-26</t>
+          <t>2021-07-27</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -27825,7 +27825,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -27887,7 +27887,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H440" s="5" t="n">
@@ -27949,7 +27949,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H441" s="5" t="n">
@@ -28011,7 +28011,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -28073,7 +28073,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -28135,7 +28135,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -28197,7 +28197,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -28259,7 +28259,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2021-07-20</t>
+          <t>2021-07-21</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -28321,7 +28321,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
@@ -28383,7 +28383,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -28507,7 +28507,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H450" s="5" t="n">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H451" s="5" t="n">
@@ -28631,7 +28631,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="H452" s="5" t="n">
@@ -28693,7 +28693,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H453" s="5" t="n">
@@ -28755,7 +28755,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
+          <t>2021-07-23</t>
         </is>
       </c>
       <c r="H454" s="5" t="n">
@@ -28817,7 +28817,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H455" s="5" t="n">
@@ -28879,7 +28879,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="H456" s="5" t="n">
@@ -28941,7 +28941,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="H457" s="5" t="n">
@@ -29003,7 +29003,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H458" s="5" t="n">
@@ -29065,7 +29065,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H459" s="5" t="n">
@@ -29127,7 +29127,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="H460" s="5" t="n">
@@ -29189,7 +29189,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="H461" s="5" t="n">
@@ -29251,7 +29251,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2021-07-10</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -29313,7 +29313,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -29375,7 +29375,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H464" s="5" t="n">
@@ -29437,7 +29437,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
@@ -29499,7 +29499,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H466" s="5" t="n">
@@ -29561,7 +29561,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H467" s="5" t="n">
@@ -29623,7 +29623,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H468" s="5" t="n">
@@ -29685,7 +29685,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2021-07-19</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -29747,7 +29747,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2021-09-05</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="H470" s="5" t="n">
@@ -29809,7 +29809,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="H471" s="5" t="n">
@@ -29871,7 +29871,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="H472" s="5" t="n">
@@ -29933,7 +29933,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="H473" s="5" t="n">
@@ -29995,7 +29995,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="H474" s="5" t="n">
@@ -30057,7 +30057,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="H475" s="5" t="n">
@@ -30119,7 +30119,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="H476" s="5" t="n">
@@ -30181,7 +30181,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H477" s="5" t="n">
@@ -30313,7 +30313,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H479" s="5" t="n">
@@ -30375,7 +30375,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H480" s="5" t="n">
@@ -30437,7 +30437,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H481" s="5" t="n">
@@ -30632,7 +30632,7 @@
           <t>A | 1350呎 (3房)
 $8355万
 $61,888/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -30651,7 +30651,7 @@
           <t>F | 505呎 (2房)
 $1370万
 $27,129/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -30659,7 +30659,7 @@
           <t>G | 380呎 (1房)
 $827万
 $21,753/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -30667,7 +30667,7 @@
           <t>H | 379呎 (1房)
 $820万
 $21,630/呎
-(25年-06月-29日)</t>
+(25年-06月-30日)</t>
         </is>
       </c>
       <c r="J5" s="22" t="inlineStr">
@@ -30690,7 +30690,7 @@
           <t>A | 890呎 (3房)
 $2996万
 $33,662/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -30714,7 +30714,7 @@
           <t>D | 546呎 (2房)
 $1950万
 $35,721/呎
-(21年-06月-02日)</t>
+(21年-06月-03日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -30722,7 +30722,7 @@
           <t>E | 695呎 (3房)
 $1557万
 $22,404/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -30730,7 +30730,7 @@
           <t>F | 505呎 (2房)
 $1437万
 $28,453/呎
-(21年-06月-02日)</t>
+(21年-06月-03日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -30738,7 +30738,7 @@
           <t>G | 380呎 (1房)
 $1055万
 $27,765/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -30746,7 +30746,7 @@
           <t>H | 379呎 (1房)
 $1058万
 $27,903/呎
-(21年-07月-13日)</t>
+(21年-07月-14日)</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
@@ -30769,7 +30769,7 @@
           <t>A | 890呎 (3房)
 $2960万
 $33,263/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -30793,7 +30793,7 @@
           <t>D | 546呎 (2房)
 $1880万
 $34,428/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -30801,7 +30801,7 @@
           <t>E | 695呎 (3房)
 $1540万
 $22,152/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -30809,7 +30809,7 @@
           <t>F | 505呎 (2房)
 $1392万
 $27,556/呎
-(21年-05月-08日)</t>
+(21年-05月-09日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -30817,7 +30817,7 @@
           <t>G | 380呎 (1房)
 $1043万
 $27,447/呎
-(22年-09月-28日)</t>
+(22年-09月-29日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -30825,7 +30825,7 @@
           <t>H | 379呎 (1房)
 $1046万
 $27,592/呎
-(21年-07月-28日)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="J7" s="22" t="inlineStr">
@@ -30848,7 +30848,7 @@
           <t>A | 890呎 (3房)
 $2943万
 $33,063/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -30872,7 +30872,7 @@
           <t>D | 546呎 (2房)
 $1887万
 $34,551/呎
-(21年-06月-07日)</t>
+(21年-06月-08日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -30880,7 +30880,7 @@
           <t>E | 695呎 (3房)
 $1528万
 $21,979/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -30888,7 +30888,7 @@
           <t>F | 505呎 (2房)
 $1425万
 $28,226/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -30896,7 +30896,7 @@
           <t>G | 380呎 (1房)
 $812万
 $21,364/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -30904,7 +30904,7 @@
           <t>H | 379呎 (1房)
 $806万
 $21,256/呎
-(25年-07月-02日)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
@@ -30927,7 +30927,7 @@
           <t>A | 890呎 (3房)
 $2934万
 $32,963/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -30943,7 +30943,7 @@
           <t>C | 550呎 (2房)
 $1965万
 $35,733/呎
-(21年-06月-22日)</t>
+(21年-06月-23日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -30951,7 +30951,7 @@
           <t>D | 546呎 (2房)
 $1881万
 $34,451/呎
-(21年-06月-15日)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -30959,7 +30959,7 @@
           <t>E | 695呎 (3房)
 $1523万
 $21,918/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -30967,7 +30967,7 @@
           <t>F | 505呎 (2房)
 $1436万
 $28,433/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -30975,7 +30975,7 @@
           <t>G | 380呎 (1房)
 $1034万
 $27,210/呎
-(23年-05月-30日)</t>
+(23年-05月-31日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -30983,7 +30983,7 @@
           <t>H | 379呎 (1房)
 $803万
 $21,196/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -30991,7 +30991,7 @@
           <t>J | 418呎 (1房)
 $1013万
 $24,241/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -31006,7 +31006,7 @@
           <t>A | 889呎 (3房)
 $3131万
 $35,222/呎
-(21年-06月-07日)</t>
+(21年-06月-08日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -31014,7 +31014,7 @@
           <t>B | 550呎 (2房)
 $1919万
 $34,896/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -31030,7 +31030,7 @@
           <t>D | 546呎 (2房)
 $1876万
 $34,351/呎
-(21年-06月-06日)</t>
+(21年-06月-07日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -31038,7 +31038,7 @@
           <t>E | 695呎 (3房)
 $1519万
 $21,855/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -31046,7 +31046,7 @@
           <t>F | 505呎 (2房)
 $1388万
 $27,492/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -31054,7 +31054,7 @@
           <t>G | 380呎 (1房)
 $807万
 $21,239/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -31062,7 +31062,7 @@
           <t>H | 379呎 (1房)
 $953万
 $25,149/呎
-(25年-05月-01日)</t>
+(25年-05月-02日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -31070,7 +31070,7 @@
           <t>J | 418呎 (1房)
 $1010万
 $24,172/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -31085,7 +31085,7 @@
           <t>A | 889呎 (3房)
 $3122万
 $35,122/呎
-(21年-07月-11日)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -31109,7 +31109,7 @@
           <t>D | 546呎 (2房)
 $1870万
 $34,250/呎
-(21年-06月-15日)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -31117,7 +31117,7 @@
           <t>E | 695呎 (3房)
 $1515万
 $21,792/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -31125,7 +31125,7 @@
           <t>F | 505呎 (2房)
 $1370万
 $27,129/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -31133,7 +31133,7 @@
           <t>G | 380呎 (1房)
 $1071万
 $28,189/呎
-(23年-04月-19日)</t>
+(23年-04月-20日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -31141,7 +31141,7 @@
           <t>H | 379呎 (1房)
 $1020万
 $26,921/呎
-(21年-07月-20日)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="J11" s="22" t="inlineStr">
@@ -31164,7 +31164,7 @@
           <t>A | 890呎 (3房)
 $2907万
 $32,663/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -31180,7 +31180,7 @@
           <t>C | 550呎 (2房)
 $1860万
 $33,823/呎
-(21年-07月-05日)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -31188,7 +31188,7 @@
           <t>D | 546呎 (2房)
 $1865万
 $34,151/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -31196,7 +31196,7 @@
           <t>E | 695呎 (3房)
 $1466万
 $21,091/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -31204,7 +31204,7 @@
           <t>F | 505呎 (2房)
 $1380万
 $27,336/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -31212,7 +31212,7 @@
           <t>G | 380呎 (1房)
 $1025万
 $26,970/呎
-(21年-08月-04日)</t>
+(21年-08月-05日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -31220,7 +31220,7 @@
           <t>H | 379呎 (1房)
 $1028万
 $27,123/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -31228,7 +31228,7 @@
           <t>J | 418呎 (1房)
 $1004万
 $24,030/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -31243,7 +31243,7 @@
           <t>A | 890呎 (3房)
 $2898万
 $32,564/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -31267,7 +31267,7 @@
           <t>D | 546呎 (2房)
 $1859万
 $34,052/呎
-(21年-07月-29日)</t>
+(21年-07月-30日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -31275,7 +31275,7 @@
           <t>E | 695呎 (3房)
 $1462万
 $21,030/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -31283,7 +31283,7 @@
           <t>F | 505呎 (2房)
 $1355万
 $26,839/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -31291,7 +31291,7 @@
           <t>G | 380呎 (1房)
 $1038万
 $27,327/呎
-(21年-05月-08日)</t>
+(21年-05月-09日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -31299,7 +31299,7 @@
           <t>H | 379呎 (1房)
 $989万
 $26,101/呎
-(21年-07月-05日)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -31307,7 +31307,7 @@
           <t>J | 418呎 (1房)
 $901万
 $21,559/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -31322,7 +31322,7 @@
           <t>A | 890呎 (3房)
 $2916万
 $32,763/呎
-(24年-07月-23日)</t>
+(24年-07月-24日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -31338,7 +31338,7 @@
           <t>C | 550呎 (2房)
 $1850万
 $33,628/呎
-(21年-06月-06日)</t>
+(21年-06月-07日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -31346,7 +31346,7 @@
           <t>D | 546呎 (2房)
 $1854万
 $33,951/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -31354,7 +31354,7 @@
           <t>E | 695呎 (3房)
 $1457万
 $20,968/呎
-(25年-06月-15日)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -31362,7 +31362,7 @@
           <t>F | 505呎 (2房)
 $1366万
 $27,043/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -31370,7 +31370,7 @@
           <t>G | 380呎 (1房)
 $994万
 $26,145/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -31378,7 +31378,7 @@
           <t>H | 379呎 (1房)
 $997万
 $26,300/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -31386,7 +31386,7 @@
           <t>J | 418呎 (1房)
 $899万
 $21,496/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -31401,7 +31401,7 @@
           <t>A | 890呎 (3房)
 $2916万
 $32,763/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -31409,7 +31409,7 @@
           <t>B | 550呎 (2房)
 $1892万
 $34,394/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -31425,7 +31425,7 @@
           <t>D | 546呎 (2房)
 $1848万
 $33,852/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -31433,7 +31433,7 @@
           <t>E | 695呎 (3房)
 $1453万
 $20,908/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -31441,7 +31441,7 @@
           <t>F | 505呎 (2房)
 $1348万
 $26,685/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -31449,7 +31449,7 @@
           <t>G | 380呎 (1房)
 $1001万
 $26,342/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -31457,7 +31457,7 @@
           <t>H | 379呎 (1房)
 $984万
 $25,951/呎
-(21年-06月-17日)</t>
+(21年-06月-18日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -31465,7 +31465,7 @@
           <t>J | 418呎 (1房)
 $896万
 $21,433/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
     </row>
@@ -31480,7 +31480,7 @@
           <t>A | 889呎 (3房)
 $3036万
 $34,145/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -31504,7 +31504,7 @@
           <t>D | 546呎 (2房)
 $1843万
 $33,751/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -31512,7 +31512,7 @@
           <t>E | 695呎 (3房)
 $1449万
 $20,848/呎
-(25年-06月-18日)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -31520,7 +31520,7 @@
           <t>F | 505呎 (2房)
 $1372万
 $27,168/呎
-(21年-05月-08日)</t>
+(21年-05月-09日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -31528,7 +31528,7 @@
           <t>G | 380呎 (1房)
 $998万
 $26,263/呎
-(21年-05月-31日)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -31536,7 +31536,7 @@
           <t>H | 379呎 (1房)
 $1001万
 $26,420/呎
-(21年-06月-15日)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -31544,7 +31544,7 @@
           <t>J | 418呎 (1房)
 $893万
 $21,370/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
     </row>
@@ -31559,7 +31559,7 @@
           <t>A | 890呎 (3房)
 $2996万
 $33,665/呎
-(21年-07月-11日)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -31567,7 +31567,7 @@
           <t>B | 550呎 (2房)
 $1875万
 $34,094/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -31583,7 +31583,7 @@
           <t>D | 546呎 (2房)
 $1832万
 $33,553/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -31591,7 +31591,7 @@
           <t>E | 695呎 (3房)
 $1440万
 $20,725/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -31599,7 +31599,7 @@
           <t>F | 505呎 (2房)
 $1336万
 $26,453/呎
-(21年-05月-31日)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -31607,7 +31607,7 @@
           <t>G | 380呎 (1房)
 $992万
 $26,107/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -31615,7 +31615,7 @@
           <t>H | 379呎 (1房)
 $985万
 $25,996/呎
-(21年-06月-06日)</t>
+(21年-06月-07日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -31623,7 +31623,7 @@
           <t>J | 418呎 (1房)
 $888万
 $21,243/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -31638,7 +31638,7 @@
           <t>A | 889呎 (3房)
 $2788万
 $31,363/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -31654,7 +31654,7 @@
           <t>C | 550呎 (2房)
 $1823万
 $33,139/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -31662,7 +31662,7 @@
           <t>D | 546呎 (2房)
 $1826万
 $33,452/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -31670,7 +31670,7 @@
           <t>E | 695呎 (3房)
 $1415万
 $20,358/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -31678,7 +31678,7 @@
           <t>F | 505呎 (2房)
 $1346万
 $26,654/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -31686,7 +31686,7 @@
           <t>G | 380呎 (1房)
 $989万
 $26,028/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -31694,7 +31694,7 @@
           <t>H | 379呎 (1房)
 $993万
 $26,190/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -31702,7 +31702,7 @@
           <t>J | 418呎 (1房)
 $885万
 $21,180/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
     </row>
@@ -31717,7 +31717,7 @@
           <t>A | 889呎 (3房)
 $3010万
 $33,857/呎
-(21年-07月-25日)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -31741,7 +31741,7 @@
           <t>D | 546呎 (2房)
 $1841万
 $33,723/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -31749,7 +31749,7 @@
           <t>E | 695呎 (3房)
 $1710万
 $24,604/呎
-(24年-12月-30日)</t>
+(24年-12月-31日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -31757,7 +31757,7 @@
           <t>F | 505呎 (2房)
 $1328万
 $26,299/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -31765,7 +31765,7 @@
           <t>G | 380呎 (1房)
 $976万
 $25,680/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -31773,7 +31773,7 @@
           <t>H | 379呎 (1房)
 $1000万
 $26,382/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -31781,7 +31781,7 @@
           <t>J | 418呎 (1房)
 $883万
 $21,119/呎
-(25年-07月-16日)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -31796,7 +31796,7 @@
           <t>A | 889呎 (3房)
 $2772万
 $31,178/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -31820,7 +31820,7 @@
           <t>D | 546呎 (2房)
 $1836万
 $33,624/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -31828,7 +31828,7 @@
           <t>E | 695呎 (3房)
 $1929万
 $27,756/呎
-(24年-01月-17日)</t>
+(24年-01月-18日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -31836,7 +31836,7 @@
           <t>F | 505呎 (2房)
 $1352万
 $26,774/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -31844,7 +31844,7 @@
           <t>G | 380呎 (1房)
 $973万
 $25,605/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -31852,7 +31852,7 @@
           <t>H | 379呎 (1房)
 $997万
 $26,305/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -31860,7 +31860,7 @@
           <t>J | 418呎 (1房)
 $880万
 $21,054/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -31875,7 +31875,7 @@
           <t>A | 890呎 (3房)
 $2936万
 $32,985/呎
-(21年-10月-05日)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -31899,7 +31899,7 @@
           <t>D | 546呎 (2房)
 $1839万
 $33,676/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -31907,7 +31907,7 @@
           <t>E | 695呎 (3房)
 $1865万
 $26,836/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -31915,7 +31915,7 @@
           <t>F | 505呎 (2房)
 $1320万
 $26,145/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -31923,7 +31923,7 @@
           <t>G | 380呎 (1房)
 $970万
 $25,527/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -31931,7 +31931,7 @@
           <t>H | 379呎 (1房)
 $974万
 $25,694/呎
-(21年-06月-10日)</t>
+(21年-06月-11日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -31939,7 +31939,7 @@
           <t>J | 418呎 (1房)
 $877万
 $20,992/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
           <t>A | 890呎 (3房)
 $2896万
 $32,544/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -31970,7 +31970,7 @@
           <t>C | 550呎 (2房)
 $1801万
 $32,747/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -31978,7 +31978,7 @@
           <t>D | 546呎 (2房)
 $1853万
 $33,932/呎
-(21年-05月-31日)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -31986,7 +31986,7 @@
           <t>E | 696呎 (3房)
 $1879万
 $26,996/呎
-(21年-08月-04日)</t>
+(21年-08月-05日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -31994,7 +31994,7 @@
           <t>F | 505呎 (2房)
 $1344万
 $26,616/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -32002,7 +32002,7 @@
           <t>G | 380呎 (1房)
 $998万
 $26,254/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -32010,7 +32010,7 @@
           <t>H | 379呎 (1房)
 $991万
 $26,152/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -32018,7 +32018,7 @@
           <t>J | 418呎 (1房)
 $885万
 $21,168/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
     </row>
@@ -32033,7 +32033,7 @@
           <t>A | 890呎 (3房)
 $2888万
 $32,446/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -32057,7 +32057,7 @@
           <t>D | 546呎 (2房)
 $1791万
 $32,805/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -32065,7 +32065,7 @@
           <t>E | 695呎 (3房)
 $1893万
 $27,231/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -32073,7 +32073,7 @@
           <t>F | 505呎 (2房)
 $1333万
 $26,395/呎
-(21年-05月-08日)</t>
+(21年-05月-09日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -32081,7 +32081,7 @@
           <t>G | 380呎 (1房)
 $974万
 $25,639/呎
-(21年-05月-31日)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -32089,7 +32089,7 @@
           <t>H | 379呎 (1房)
 $968万
 $25,542/呎
-(21年-05月-31日)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -32097,7 +32097,7 @@
           <t>J | 418呎 (1房)
 $872万
 $20,866/呎
-(25年-07月-01日)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -32112,7 +32112,7 @@
           <t>A | 889呎 (3房)
 $2795万
 $31,437/呎
-(21年-05月-31日)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -32136,7 +32136,7 @@
           <t>D | 546呎 (2房)
 $1767万
 $32,364/呎
-(21年-05月-25日)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -32144,7 +32144,7 @@
           <t>E | 696呎 (3房)
 $1906万
 $27,389/呎
-(21年-05月-08日)</t>
+(21年-05月-09日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -32152,7 +32152,7 @@
           <t>F | 505呎 (2房)
 $1315万
 $26,043/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -32160,7 +32160,7 @@
           <t>G | 380呎 (1房)
 $992万
 $26,094/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -32168,7 +32168,7 @@
           <t>H | 379呎 (1房)
 $955万
 $25,201/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -32176,7 +32176,7 @@
           <t>J | 418呎 (1房)
 $1111万
 $26,570/呎
-(23年-02月-28日)</t>
+(23年-03月-01日)</t>
         </is>
       </c>
     </row>
@@ -32191,7 +32191,7 @@
           <t>A | 889呎 (3房)
 $2854万
 $32,098/呎
-(21年-05月-25日)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -32215,7 +32215,7 @@
           <t>D | 546呎 (2房)
 $1786万
 $32,705/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -32223,7 +32223,7 @@
           <t>E | 695呎 (3房)
 $1685万
 $24,242/呎
-(25年-04月-01日)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -32231,7 +32231,7 @@
           <t>F | 505呎 (2房)
 $1329万
 $26,317/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -32239,7 +32239,7 @@
           <t>G | 380呎 (1房)
 $971万
 $25,561/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -32247,7 +32247,7 @@
           <t>H | 379呎 (1房)
 $985万
 $25,997/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -32255,7 +32255,7 @@
           <t>J | 418呎 (1房)
 $869万
 $20,801/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -32270,7 +32270,7 @@
           <t>A | 890呎 (3房)
 $2842万
 $31,933/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -32294,7 +32294,7 @@
           <t>D | 546呎 (2房)
 $1762万
 $32,267/呎
-(21年-05月-25日)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -32302,7 +32302,7 @@
           <t>E | 696呎 (3房)
 $1862万
 $26,754/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -32310,7 +32310,7 @@
           <t>F | 505呎 (2房)
 $1325万
 $26,237/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -32318,7 +32318,7 @@
           <t>G | 380呎 (1房)
 $989万
 $26,014/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -32326,7 +32326,7 @@
           <t>H | 379呎 (1房)
 $962万
 $25,391/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -32334,7 +32334,7 @@
           <t>J | 418呎 (1房)
 $867万
 $20,740/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -32349,7 +32349,7 @@
           <t>A | 890呎 (3房)
 $2833万
 $31,837/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -32373,7 +32373,7 @@
           <t>D | 546呎 (2房)
 $1775万
 $32,506/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -32381,7 +32381,7 @@
           <t>E | 695呎 (3房)
 $1809万
 $26,030/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -32389,7 +32389,7 @@
           <t>F | 505呎 (2房)
 $1275万
 $25,244/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -32397,7 +32397,7 @@
           <t>G | 380呎 (1房)
 $975万
 $25,669/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -32405,7 +32405,7 @@
           <t>H | 379呎 (1房)
 $959万
 $25,315/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -32413,7 +32413,7 @@
           <t>J | 418呎 (1房)
 $899万
 $21,502/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -32428,7 +32428,7 @@
           <t>A | 890呎 (3房)
 $2825万
 $31,741/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -32452,7 +32452,7 @@
           <t>D | 546呎 (2房)
 $1788万
 $32,745/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -32460,7 +32460,7 @@
           <t>E | 696呎 (3房)
 $1823万
 $26,188/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -32468,7 +32468,7 @@
           <t>F | 505呎 (2房)
 $1284万
 $25,433/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -32476,7 +32476,7 @@
           <t>G | 380呎 (1房)
 $962万
 $25,326/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -32484,7 +32484,7 @@
           <t>H | 379呎 (1房)
 $966万
 $25,501/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
@@ -32492,7 +32492,7 @@
           <t>J | 418呎 (1房)
 $871万
 $20,848/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -32507,7 +32507,7 @@
           <t>A | 890呎 (3房)
 $2905万
 $32,636/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -32539,7 +32539,7 @@
           <t>E | 695呎 (3房)
 $1684万
 $24,225/呎
-(24年-05月-07日)</t>
+(24年-05月-08日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -32547,7 +32547,7 @@
           <t>F | 505呎 (2房)
 $1294万
 $25,619/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -32555,7 +32555,7 @@
           <t>G | 380呎 (1房)
 $949万
 $24,985/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -32563,7 +32563,7 @@
           <t>H | 379呎 (1房)
 $954万
 $25,163/呎
-(21年-06月-16日)</t>
+(21年-06月-17日)</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
@@ -32571,7 +32571,7 @@
           <t>J | 418呎 (1房)
 $859万
 $20,552/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -32610,7 +32610,7 @@
           <t>D | 546呎 (2房)
 $1693万
 $31,004/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -32618,7 +32618,7 @@
           <t>E | 695呎 (3房)
 $1866万
 $26,854/呎
-(24年-01月-01日)</t>
+(24年-01月-02日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -32626,7 +32626,7 @@
           <t>F | 505呎 (2房)
 $1260万
 $24,941/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -32634,7 +32634,7 @@
           <t>G | 380呎 (1房)
 $944万
 $24,830/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -32642,7 +32642,7 @@
           <t>H | 379呎 (1房)
 $968万
 $25,532/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="J30" s="22" t="inlineStr">
@@ -32663,8 +32663,8 @@
       <c r="B31" s="24" t="inlineStr">
         <is>
           <t>A | 889呎 (3房)
-万
-,241/呎
+$279630002866万
+$3,145,444,351,701/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -32689,7 +32689,7 @@
           <t>D | 546呎 (2房)
 $1723万
 $31,559/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -32697,7 +32697,7 @@
           <t>E | 695呎 (3房)
 $1644万
 $23,661/呎
-(24年-07月-14日)</t>
+(24年-07月-15日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -32705,7 +32705,7 @@
           <t>F | 505呎 (2房)
 $1256万
 $24,866/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -32713,7 +32713,7 @@
           <t>G | 380呎 (1房)
 $970万
 $25,534/呎
-(21年-05月-08日)</t>
+(21年-05月-09日)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -32721,7 +32721,7 @@
           <t>H | 379呎 (1房)
 $965万
 $25,454/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
@@ -32729,7 +32729,7 @@
           <t>J | 417呎 (1房)
 $1077万
 $25,828/呎
-(21年-08月-05日)</t>
+(21年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -32776,7 +32776,7 @@
           <t>E | 695呎 (3房)
 $1357万
 $19,521/呎
-(25年-06月-17日)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -32784,7 +32784,7 @@
           <t>F | 505呎 (2房)
 $1295万
 $25,651/呎
-(21年-05月-08日)</t>
+(21年-05月-09日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -32792,7 +32792,7 @@
           <t>G | 380呎 (1房)
 $950万
 $25,013/呎
-(21年-06月-15日)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -32800,7 +32800,7 @@
           <t>H | 379呎 (1房)
 $965万
 $25,454/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="J32" s="20" t="inlineStr">
@@ -32808,7 +32808,7 @@
           <t>J | 418呎 (1房)
 $1088万
 $26,034/呎
-(23年-04月-27日)</t>
+(23年-04月-28日)</t>
         </is>
       </c>
     </row>
@@ -32855,7 +32855,7 @@
           <t>E | 695呎 (3房)
 $1639万
 $23,588/呎
-(24年-05月-05日)</t>
+(24年-05月-06日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -32863,7 +32863,7 @@
           <t>F | 505呎 (2房)
 $1252万
 $24,788/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -32871,7 +32871,7 @@
           <t>G | 380呎 (1房)
 $967万
 $25,454/呎
-(21年-06月-20日)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
@@ -32879,7 +32879,7 @@
           <t>H | 379呎 (1房)
 $972万
 $25,635/呎
-(21年-06月-02日)</t>
+(21年-06月-03日)</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
@@ -32887,7 +32887,7 @@
           <t>J | 418呎 (1房)
 $832万
 $19,899/呎
-(25年-07月-28日)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
           <t>E | 695呎 (3房)
 $1849万
 $26,610/呎
-(24年-04月-11日)</t>
+(24年-04月-12日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -32942,7 +32942,7 @@
           <t>F | 505呎 (2房)
 $1240万
 $24,563/呎
-(21年-06月-02日)</t>
+(21年-06月-03日)</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -32950,7 +32950,7 @@
           <t>G | 380呎 (1房)
 $929万
 $24,442/呎
-(21年-06月-17日)</t>
+(21年-06月-18日)</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr">
@@ -32958,7 +32958,7 @@
           <t>H | 379呎 (1房)
 $953万
 $25,151/呎
-(21年-05月-08日)</t>
+(21年-05月-09日)</t>
         </is>
       </c>
       <c r="J34" s="20" t="inlineStr">
@@ -32966,7 +32966,7 @@
           <t>J | 418呎 (1房)
 $824万
 $19,711/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
     </row>
@@ -33013,7 +33013,7 @@
           <t>E | 695呎 (3房)
 $1364万
 $19,633/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -33021,7 +33021,7 @@
           <t>F | 505呎 (2房)
 $1279万
 $25,328/呎
-(21年-06月-15日)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr">
@@ -33029,7 +33029,7 @@
           <t>G | 380呎 (1房)
 $988万
 $25,996/呎
-(21年-07月-04日)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
@@ -33037,7 +33037,7 @@
           <t>H | 379呎 (1房)
 $973万
 $25,665/呎
-(21年-08月-02日)</t>
+(21年-08月-03日)</t>
         </is>
       </c>
       <c r="J35" s="20" t="inlineStr">
@@ -33045,7 +33045,7 @@
           <t>J | 418呎 (1房)
 $840万
 $20,089/呎
-(25年-06月-13日)</t>
+(25年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -33092,7 +33092,7 @@
           <t>E | 695呎 (3房)
 $1387万
 $19,958/呎
-(25年-06月-11日)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr">
@@ -33100,7 +33100,7 @@
           <t>F | 505呎 (2房)
 $1315万
 $26,047/呎
-(21年-06月-10日)</t>
+(21年-06月-11日)</t>
         </is>
       </c>
       <c r="H36" s="20" t="inlineStr">
@@ -33108,7 +33108,7 @@
           <t>G | 380呎 (1房)
 $965万
 $25,384/呎
-(21年-07月-13日)</t>
+(21年-07月-14日)</t>
         </is>
       </c>
       <c r="I36" s="20" t="inlineStr">
@@ -33116,7 +33116,7 @@
           <t>H | 379呎 (1房)
 $960万
 $25,322/呎
-(21年-08月-03日)</t>
+(21年-08月-04日)</t>
         </is>
       </c>
       <c r="J36" s="20" t="inlineStr">
@@ -33124,7 +33124,7 @@
           <t>J | 418呎 (1房)
 $814万
 $19,468/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
     </row>
@@ -33171,7 +33171,7 @@
           <t>E | 695呎 (3房)
 $1371万
 $19,722/呎
-(25年-06月-11日)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr">
@@ -33179,7 +33179,7 @@
           <t>F | 505呎 (2房)
 $1280万
 $25,355/呎
-(21年-06月-20日)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="H37" s="20" t="inlineStr">
@@ -33187,7 +33187,7 @@
           <t>G | 380呎 (1房)
 $948万
 $24,957/呎
-(21年-07月-18日)</t>
+(21年-07月-19日)</t>
         </is>
       </c>
       <c r="I37" s="20" t="inlineStr">
@@ -33195,7 +33195,7 @@
           <t>H | 379呎 (1房)
 $984万
 $25,951/呎
-(21年-08月-30日)</t>
+(21年-08月-31日)</t>
         </is>
       </c>
       <c r="J37" s="20" t="inlineStr">
@@ -33203,7 +33203,7 @@
           <t>J | 418呎 (1房)
 $809万
 $19,344/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -33222,7 +33222,7 @@
           <t>E | 705呎 (3房)
 $1357万
 $19,241/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr">
@@ -33230,7 +33230,7 @@
           <t>F | 505呎 (2房)
 $1312万
 $25,985/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="H38" s="20" t="inlineStr">
@@ -33238,7 +33238,7 @@
           <t>G | 380呎 (1房)
 $952万
 $25,058/呎
-(23年-12月-21日)</t>
+(23年-12月-22日)</t>
         </is>
       </c>
       <c r="I38" s="20" t="inlineStr">
@@ -33246,7 +33246,7 @@
           <t>H | 379呎 (1房)
 $938万
 $24,747/呎
-(22年-09月-07日)</t>
+(22年-09月-08日)</t>
         </is>
       </c>
       <c r="J38" s="20" t="inlineStr">
@@ -33254,7 +33254,7 @@
           <t>J | 418呎 (1房)
 $817万
 $19,552/呎
-(25年-07月-28日)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -33416,7 +33416,7 @@
           <t>A | 320呎 (1房)
 $876万
 $27,366/呎
-(21年-06月-14日)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -33424,7 +33424,7 @@
           <t>B | 296呎 (1房)
 $819万
 $27,653/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -33432,7 +33432,7 @@
           <t>C | 321呎 (1房)
 $870万
 $27,098/呎
-(21年-06月-24日)</t>
+(21年-06月-25日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -33440,7 +33440,7 @@
           <t>D | 331呎 (1房)
 $878万
 $26,537/呎
-(21年-06月-29日)</t>
+(21年-06月-30日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -33448,7 +33448,7 @@
           <t>E | 301呎 (1房)
 $810万
 $26,915/呎
-(21年-06月-29日)</t>
+(21年-06月-30日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -33456,7 +33456,7 @@
           <t>F | 301呎 (1房)
 $835万
 $27,749/呎
-(21年-07月-14日)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -33464,7 +33464,7 @@
           <t>G | 208呎 (开放式)
 $595万
 $28,614/呎
-(21年-08月-03日)</t>
+(21年-08月-04日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -33472,7 +33472,7 @@
           <t>H | 216呎 (开放式)
 $627万
 $29,040/呎
-(21年-09月-02日)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
           <t>A | 320呎 (1房)
 $856万
 $26,757/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -33495,7 +33495,7 @@
           <t>B | 296呎 (1房)
 $776万
 $26,228/呎
-(21年-06月-06日)</t>
+(21年-06月-07日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -33503,7 +33503,7 @@
           <t>C | 321呎 (1房)
 $860万
 $26,780/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -33511,7 +33511,7 @@
           <t>D | 330呎 (1房)
 $886万
 $26,851/呎
-(21年-07月-22日)</t>
+(21年-07月-23日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -33519,7 +33519,7 @@
           <t>E | 301呎 (1房)
 $817万
 $27,147/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -33527,7 +33527,7 @@
           <t>F | 302呎 (1房)
 $817万
 $27,047/呎
-(21年-07月-05日)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -33535,7 +33535,7 @@
           <t>G | 208呎 (开放式)
 $607万
 $29,183/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -33543,7 +33543,7 @@
           <t>H | 216呎 (开放式)
 $620万
 $28,702/呎
-(21年-08月-02日)</t>
+(21年-08月-03日)</t>
         </is>
       </c>
     </row>
@@ -33558,7 +33558,7 @@
           <t>A | 320呎 (1房)
 $857万
 $26,793/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -33566,7 +33566,7 @@
           <t>B | 296呎 (1房)
 $769万
 $25,993/呎
-(21年-06月-08日)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -33574,7 +33574,7 @@
           <t>C | 321呎 (1房)
 $835万
 $25,998/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -33582,7 +33582,7 @@
           <t>D | 330呎 (1房)
 $869万
 $26,336/呎
-(21年-07月-19日)</t>
+(21年-07月-20日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -33590,7 +33590,7 @@
           <t>E | 302呎 (1房)
 $810万
 $26,814/呎
-(21年-06月-10日)</t>
+(21年-06月-11日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -33598,7 +33598,7 @@
           <t>F | 302呎 (1房)
 $818万
 $27,083/呎
-(21年-07月-07日)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -33606,7 +33606,7 @@
           <t>G | 208呎 (开放式)
 $600万
 $28,826/呎
-(21年-06月-10日)</t>
+(21年-06月-11日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -33614,7 +33614,7 @@
           <t>H | 216呎 (开放式)
 $627万
 $29,041/呎
-(21年-06月-08日)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -33629,7 +33629,7 @@
           <t>A | 320呎 (1房)
 $841万
 $26,270/呎
-(21年-06月-29日)</t>
+(21年-06月-30日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -33637,7 +33637,7 @@
           <t>B | 296呎 (1房)
 $771万
 $26,033/呎
-(21年-06月-06日)</t>
+(21年-06月-07日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -33645,7 +33645,7 @@
           <t>C | 321呎 (1房)
 $844万
 $26,301/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -33653,7 +33653,7 @@
           <t>D | 331呎 (1房)
 $861万
 $26,018/呎
-(21年-07月-20日)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -33661,7 +33661,7 @@
           <t>E | 301呎 (1房)
 $802万
 $26,655/呎
-(21年-06月-20日)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -33669,7 +33669,7 @@
           <t>F | 301呎 (1房)
 $794万
 $26,373/呎
-(21年-07月-15日)</t>
+(21年-07月-16日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -33677,7 +33677,7 @@
           <t>G | 208呎 (开放式)
 $578万
 $27,797/呎
-(21年-08月-05日)</t>
+(21年-08月-06日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -33685,7 +33685,7 @@
           <t>H | 216呎 (开放式)
 $615万
 $28,489/呎
-(21年-08月-19日)</t>
+(21年-08月-20日)</t>
         </is>
       </c>
     </row>
@@ -33700,7 +33700,7 @@
           <t>A | 299呎 (1房)
 $862万
 $28,823/呎
-(21年-06月-24日)</t>
+(21年-06月-25日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -33708,7 +33708,7 @@
           <t>B | 272呎 (1房)
 $967万
 $35,561/呎
-(21年-05月-28日)</t>
+(21年-05月-29日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -33716,7 +33716,7 @@
           <t>C | 299呎 (1房)
 $823万
 $27,535/呎
-(21年-06月-22日)</t>
+(21年-06月-23日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -33724,7 +33724,7 @@
           <t>D | 330呎 (1房)
 $844万
 $25,587/呎
-(21年-07月-09日)</t>
+(21年-07月-10日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -33732,7 +33732,7 @@
           <t>E | 302呎 (1房)
 $779万
 $25,786/呎
-(21年-06月-24日)</t>
+(21年-06月-25日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -33740,7 +33740,7 @@
           <t>F | 302呎 (1房)
 $803万
 $26,586/呎
-(21年-07月-15日)</t>
+(21年-07月-16日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -33748,7 +33748,7 @@
           <t>G | 208呎 (开放式)
 $573万
 $27,554/呎
-(21年-09月-08日)</t>
+(21年-09月-09日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -33756,7 +33756,7 @@
           <t>H | 216呎 (开放式)
 $597万
 $27,651/呎
-(21年-09月-01日)</t>
+(21年-09月-02日)</t>
         </is>
       </c>
     </row>
@@ -33774,7 +33774,7 @@
           <t>D | 309呎 (1房)
 $995万
 $32,200/呎
-(21年-07月-15日)</t>
+(21年-07月-16日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -33782,7 +33782,7 @@
           <t>E | 280呎 (1房)
 $920万
 $32,858/呎
-(21年-06月-07日)</t>
+(21年-06月-08日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -33790,7 +33790,7 @@
           <t>F | 280呎 (1房)
 $910万
 $32,510/呎
-(21年-07月-04日)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -33798,7 +33798,7 @@
           <t>G | 186呎 (开放式)
 $682万
 $36,655/呎
-(21年-06月-24日)</t>
+(21年-06月-25日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -33806,7 +33806,7 @@
           <t>H | 195呎 (开放式)
 $567万
 $29,100/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
     </row>
@@ -33968,7 +33968,7 @@
           <t>A | 320呎 (1房)
 $899万
 $28,107/呎
-(21年-06月-15日)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -33976,7 +33976,7 @@
           <t>B | 296呎 (1房)
 $815万
 $27,545/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -33984,7 +33984,7 @@
           <t>C | 321呎 (1房)
 $873万
 $27,204/呎
-(21年-07月-19日)</t>
+(21年-07月-20日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -33992,7 +33992,7 @@
           <t>D | 330呎 (1房)
 $701万
 $21,238/呎
-(25年-07月-08日)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -34000,7 +34000,7 @@
           <t>E | 301呎 (1房)
 $825万
 $27,414/呎
-(21年-07月-18日)</t>
+(21年-07月-19日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -34008,7 +34008,7 @@
           <t>F | 301呎 (1房)
 $834万
 $27,703/呎
-(21年-06月-22日)</t>
+(21年-06月-23日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -34016,7 +34016,7 @@
           <t>G | 208呎 (开放式)
 $613万
 $29,473/呎
-(21年-06月-15日)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -34024,7 +34024,7 @@
           <t>H | 216呎 (开放式)
 $645万
 $29,867/呎
-(21年-07月-05日)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -34039,7 +34039,7 @@
           <t>A | 320呎 (1房)
 $879万
 $27,482/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -34047,7 +34047,7 @@
           <t>B | 296呎 (1房)
 $806万
 $27,224/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -34055,7 +34055,7 @@
           <t>C | 321呎 (1房)
 $890万
 $27,733/呎
-(21年-07月-19日)</t>
+(21年-07月-20日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -34063,7 +34063,7 @@
           <t>D | 330呎 (1房)
 $692万
 $20,984/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -34071,7 +34071,7 @@
           <t>E | 302呎 (1房)
 $824万
 $27,283/呎
-(21年-07月-07日)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -34079,7 +34079,7 @@
           <t>F | 301呎 (1房)
 $841万
 $27,945/呎
-(21年-06月-17日)</t>
+(21年-06月-18日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -34087,7 +34087,7 @@
           <t>G | 208呎 (开放式)
 $593万
 $28,518/呎
-(21年-06月-15日)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -34095,7 +34095,7 @@
           <t>H | 216呎 (开放式)
 $644万
 $29,824/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -34110,7 +34110,7 @@
           <t>A | 320呎 (1房)
 $872万
 $27,235/呎
-(21年-06月-17日)</t>
+(21年-06月-18日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -34118,7 +34118,7 @@
           <t>B | 296呎 (1房)
 $799万
 $26,984/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -34126,7 +34126,7 @@
           <t>C | 321呎 (1房)
 $882万
 $27,489/呎
-(21年-07月-06日)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -34134,7 +34134,7 @@
           <t>D | 330呎 (1房)
 $698万
 $21,152/呎
-(25年-06月-08日)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -34142,7 +34142,7 @@
           <t>E | 302呎 (1房)
 $808万
 $26,757/呎
-(21年-07月-06日)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -34150,7 +34150,7 @@
           <t>F | 301呎 (1房)
 $817万
 $27,129/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -34158,7 +34158,7 @@
           <t>G | 208呎 (开放式)
 $588万
 $28,258/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -34166,7 +34166,7 @@
           <t>H | 216呎 (开放式)
 $632万
 $29,268/呎
-(21年-06月-16日)</t>
+(21年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -34181,7 +34181,7 @@
           <t>A | 320呎 (1房)
 $891万
 $27,838/呎
-(21年-06月-17日)</t>
+(21年-06月-18日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -34189,7 +34189,7 @@
           <t>B | 296呎 (1房)
 $808万
 $27,301/呎
-(21年-06月-16日)</t>
+(21年-06月-17日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -34197,7 +34197,7 @@
           <t>C | 321呎 (1房)
 $848万
 $26,407/呎
-(21年-07月-06日)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -34205,7 +34205,7 @@
           <t>D | 330呎 (1房)
 $680万
 $20,608/呎
-(25年-06月-29日)</t>
+(25年-06月-30日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -34213,7 +34213,7 @@
           <t>E | 302呎 (1房)
 $826万
 $27,349/呎
-(21年-07月-14日)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -34221,7 +34221,7 @@
           <t>F | 301呎 (1房)
 $809万
 $26,880/呎
-(21年-07月-22日)</t>
+(21年-07月-23日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -34229,7 +34229,7 @@
           <t>G | 208呎 (开放式)
 $601万
 $28,886/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -34237,7 +34237,7 @@
           <t>H | 216呎 (开放式)
 $627万
 $29,010/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -34252,7 +34252,7 @@
           <t>A | 299呎 (1房)
 $876万
 $29,307/呎
-(21年-07月-04日)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -34260,7 +34260,7 @@
           <t>B | 272呎 (1房)
 $789万
 $29,008/呎
-(21年-07月-04日)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -34268,7 +34268,7 @@
           <t>C | 299呎 (1房)
 $853万
 $28,527/呎
-(21年-07月-20日)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -34276,7 +34276,7 @@
           <t>D | 331呎 (1房)
 $870万
 $26,277/呎
-(21年-07月-28日)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -34284,7 +34284,7 @@
           <t>E | 302呎 (1房)
 $818万
 $27,099/呎
-(21年-07月-18日)</t>
+(21年-07月-19日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -34292,7 +34292,7 @@
           <t>F | 302呎 (1房)
 $793万
 $26,270/呎
-(21年-07月-15日)</t>
+(21年-07月-16日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -34300,7 +34300,7 @@
           <t>G | 208呎 (开放式)
 $583万
 $28,034/呎
-(21年-06月-22日)</t>
+(21年-06月-23日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -34308,7 +34308,7 @@
           <t>H | 216呎 (开放式)
 $608万
 $28,164/呎
-(21年-09月-07日)</t>
+(21年-09月-08日)</t>
         </is>
       </c>
     </row>
@@ -34326,7 +34326,7 @@
           <t>D | 309呎 (1房)
 $1022万
 $33,087/呎
-(21年-08月-25日)</t>
+(21年-08月-26日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -34334,7 +34334,7 @@
           <t>E | 280呎 (1房)
 $806万
 $28,800/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -34342,7 +34342,7 @@
           <t>F | 280呎 (1房)
 $740万
 $26,421/呎
-(26年-01月-14日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -34350,7 +34350,7 @@
           <t>G | 186呎 (开放式)
 $513万
 $27,581/呎
-(25年-07月-20日)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -34358,7 +34358,7 @@
           <t>H | 195呎 (开放式)
 $623万
 $31,935/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -34520,7 +34520,7 @@
           <t>A | 320呎 (1房)
 $898万
 $28,074/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -34528,7 +34528,7 @@
           <t>B | 296呎 (1房)
 $806万
 $27,229/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -34536,7 +34536,7 @@
           <t>C | 321呎 (1房)
 $856万
 $26,679/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -34544,7 +34544,7 @@
           <t>D | 331呎 (1房)
 $898万
 $27,129/呎
-(21年-07月-18日)</t>
+(21年-07月-19日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -34552,7 +34552,7 @@
           <t>E | 302呎 (1房)
 $828万
 $27,411/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -34560,7 +34560,7 @@
           <t>F | 302呎 (1房)
 $836万
 $27,690/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -34568,7 +34568,7 @@
           <t>G | 208呎 (开放式)
 $614万
 $29,518/呎
-(21年-07月-28日)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -34576,7 +34576,7 @@
           <t>H | 216呎 (开放式)
 $634万
 $29,342/呎
-(21年-06月-19日)</t>
+(21年-06月-20日)</t>
         </is>
       </c>
     </row>
@@ -34591,7 +34591,7 @@
           <t>A | 320呎 (1房)
 $870万
 $27,174/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -34599,7 +34599,7 @@
           <t>B | 296呎 (1房)
 $788万
 $26,636/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -34607,7 +34607,7 @@
           <t>C | 321呎 (1房)
 $846万
 $26,365/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -34615,7 +34615,7 @@
           <t>D | 330呎 (1房)
 $878万
 $26,613/呎
-(21年-07月-02日)</t>
+(21年-07月-03日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -34623,7 +34623,7 @@
           <t>E | 301呎 (1房)
 $810万
 $26,896/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -34631,7 +34631,7 @@
           <t>F | 301呎 (1房)
 $801万
 $26,618/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -34639,7 +34639,7 @@
           <t>G | 208呎 (开放式)
 $588万
 $28,290/呎
-(21年-07月-12日)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -34647,7 +34647,7 @@
           <t>H | 216呎 (开放式)
 $633万
 $29,300/呎
-(21年-07月-22日)</t>
+(21年-07月-23日)</t>
         </is>
       </c>
     </row>
@@ -34662,7 +34662,7 @@
           <t>A | 320呎 (1房)
 $880万
 $27,489/呎
-(21年-05月-19日)</t>
+(21年-05月-20日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -34670,7 +34670,7 @@
           <t>B | 296呎 (1房)
 $806万
 $27,225/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -34678,7 +34678,7 @@
           <t>C | 321呎 (1房)
 $856万
 $26,674/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -34686,7 +34686,7 @@
           <t>D | 330呎 (1房)
 $879万
 $26,644/呎
-(21年-07月-19日)</t>
+(21年-07月-20日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -34694,7 +34694,7 @@
           <t>E | 302呎 (1房)
 $794万
 $26,292/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -34702,7 +34702,7 @@
           <t>F | 302呎 (1房)
 $811万
 $26,839/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -34710,7 +34710,7 @@
           <t>G | 208呎 (开放式)
 $608万
 $29,224/呎
-(21年-07月-18日)</t>
+(21年-07月-19日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -34718,7 +34718,7 @@
           <t>H | 216呎 (开放式)
 $608万
 $28,152/呎
-(21年-07月-20日)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
     </row>
@@ -34733,7 +34733,7 @@
           <t>A | 320呎 (1房)
 $863万
 $26,960/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -34741,7 +34741,7 @@
           <t>B | 296呎 (1房)
 $766万
 $25,891/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -34749,7 +34749,7 @@
           <t>C | 321呎 (1房)
 $840万
 $26,163/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -34757,7 +34757,7 @@
           <t>D | 331呎 (1房)
 $844万
 $25,512/呎
-(21年-07月-18日)</t>
+(21年-07月-19日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -34765,7 +34765,7 @@
           <t>E | 302呎 (1房)
 $795万
 $26,322/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -34773,7 +34773,7 @@
           <t>F | 302呎 (1房)
 $787万
 $26,050/呎
-(21年-07月-05日)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -34781,7 +34781,7 @@
           <t>G | 208呎 (开放式)
 $596万
 $28,674/呎
-(21年-07月-18日)</t>
+(21年-07月-19日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -34789,7 +34789,7 @@
           <t>H | 216呎 (开放式)
 $609万
 $28,195/呎
-(21年-07月-15日)</t>
+(21年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -34804,7 +34804,7 @@
           <t>A | 299呎 (1房)
 $840万
 $28,084/呎
-(21年-05月-31日)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -34812,7 +34812,7 @@
           <t>B | 274呎 (1房)
 $790万
 $28,842/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -34820,7 +34820,7 @@
           <t>C | 299呎 (1房)
 $836万
 $27,961/呎
-(21年-05月-31日)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -34828,7 +34828,7 @@
           <t>D | 330呎 (1房)
 $655万
 $19,852/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -34836,7 +34836,7 @@
           <t>E | 301呎 (1房)
 $771万
 $25,625/呎
-(21年-07月-15日)</t>
+(21年-07月-16日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -34844,7 +34844,7 @@
           <t>F | 302呎 (1房)
 $796万
 $26,346/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -34852,7 +34852,7 @@
           <t>G | 208呎 (开放式)
 $573万
 $27,554/呎
-(21年-08月-04日)</t>
+(21年-08月-05日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -34860,7 +34860,7 @@
           <t>H | 216呎 (开放式)
 $597万
 $27,651/呎
-(21年-08月-11日)</t>
+(21年-08月-12日)</t>
         </is>
       </c>
     </row>
@@ -34878,7 +34878,7 @@
           <t>D | 309呎 (1房)
 $980万
 $31,722/呎
-(23年-05月-09日)</t>
+(23年-05月-10日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -34886,7 +34886,7 @@
           <t>E | 280呎 (1房)
 $806万
 $28,800/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -34894,7 +34894,7 @@
           <t>F | 280呎 (1房)
 $806万
 $28,800/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -34902,7 +34902,7 @@
           <t>G | 186呎 (开放式)
 $683万
 $36,718/呎
-(21年-07月-18日)</t>
+(21年-07月-19日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -34910,7 +34910,7 @@
           <t>H | 194呎 (开放式)
 $708万
 $36,472/呎
-(21年-08月-10日)</t>
+(21年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -35072,7 +35072,7 @@
           <t>A | 320呎 (1房)
 $868万
 $27,114/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -35080,7 +35080,7 @@
           <t>B | 296呎 (1房)
 $823万
 $27,788/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -35088,7 +35088,7 @@
           <t>C | 321呎 (1房)
 $871万
 $27,122/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -35096,7 +35096,7 @@
           <t>D | 331呎 (1房)
 $853万
 $25,773/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -35104,7 +35104,7 @@
           <t>E | 301呎 (1房)
 $786万
 $26,127/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -35112,7 +35112,7 @@
           <t>F | 299呎 (1房)
 $778万
 $26,025/呎
-(21年-05月-08日)</t>
+(21年-05月-09日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -35120,7 +35120,7 @@
           <t>G | 207呎 (开放式)
 $605万
 $29,211/呎
-(21年-07月-26日)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -35128,7 +35128,7 @@
           <t>H | 321呎 (1房)
 $883万
 $27,510/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -35143,7 +35143,7 @@
           <t>A | 320呎 (1房)
 $857万
 $26,790/呎
-(21年-05月-08日)</t>
+(21年-05月-09日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -35151,7 +35151,7 @@
           <t>B | 296呎 (1房)
 $821万
 $27,740/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -35159,7 +35159,7 @@
           <t>C | 321呎 (1房)
 $852万
 $26,534/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -35167,7 +35167,7 @@
           <t>D | 330呎 (1房)
 $870万
 $26,350/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -35175,7 +35175,7 @@
           <t>E | 301呎 (1房)
 $793万
 $26,357/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -35183,7 +35183,7 @@
           <t>F | 299呎 (1房)
 $777万
 $25,994/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -35191,7 +35191,7 @@
           <t>G | 207呎 (开放式)
 $597万
 $28,862/呎
-(21年-07月-20日)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -35199,7 +35199,7 @@
           <t>H | 321呎 (1房)
 $855万
 $26,629/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -35214,7 +35214,7 @@
           <t>A | 320呎 (1房)
 $841万
 $26,273/呎
-(21年-05月-08日)</t>
+(21年-05月-09日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -35222,7 +35222,7 @@
           <t>B | 296呎 (1房)
 $781万
 $26,382/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -35230,7 +35230,7 @@
           <t>C | 321呎 (1房)
 $853万
 $26,570/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -35238,7 +35238,7 @@
           <t>D | 331呎 (1房)
 $835万
 $25,234/呎
-(21年-05月-08日)</t>
+(21年-05月-09日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -35246,7 +35246,7 @@
           <t>E | 301呎 (1房)
 $770万
 $25,580/呎
-(21年-05月-08日)</t>
+(21年-05月-09日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -35254,7 +35254,7 @@
           <t>F | 299呎 (1房)
 $794万
 $26,571/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -35262,7 +35262,7 @@
           <t>G | 207呎 (开放式)
 $598万
 $28,906/呎
-(21年-07月-22日)</t>
+(21年-07月-23日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -35270,7 +35270,7 @@
           <t>H | 321呎 (1房)
 $873万
 $27,211/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
     </row>
@@ -35285,7 +35285,7 @@
           <t>A | 320呎 (1房)
 $841万
 $26,294/呎
-(21年-07月-11日)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -35293,7 +35293,7 @@
           <t>B | 296呎 (1房)
 $798万
 $26,967/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -35301,7 +35301,7 @@
           <t>C | 321呎 (1房)
 $819万
 $25,529/呎
-(21年-05月-25日)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -35309,7 +35309,7 @@
           <t>D | 330呎 (1房)
 $836万
 $25,344/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -35317,7 +35317,7 @@
           <t>E | 302呎 (1房)
 $787万
 $26,061/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -35325,7 +35325,7 @@
           <t>F | 299呎 (1房)
 $763万
 $25,534/呎
-(21年-05月-08日)</t>
+(21年-05月-09日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -35333,7 +35333,7 @@
           <t>G | 207呎 (开放式)
 $605万
 $29,239/呎
-(21年-07月-09日)</t>
+(21年-07月-10日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -35341,7 +35341,7 @@
           <t>H | 321呎 (1房)
 $857万
 $26,692/呎
-(21年-05月-08日)</t>
+(21年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -35356,7 +35356,7 @@
           <t>A | 298呎 (1房)
 $838万
 $28,108/呎
-(21年-07月-18日)</t>
+(21年-07月-19日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -35364,7 +35364,7 @@
           <t>B | 272呎 (1房)
 $795万
 $29,231/呎
-(21年-06月-02日)</t>
+(21年-06月-03日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -35372,7 +35372,7 @@
           <t>C | 299呎 (1房)
 $824万
 $27,563/呎
-(21年-07月-28日)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -35380,7 +35380,7 @@
           <t>D | 330呎 (1房)
 $828万
 $25,094/呎
-(21年-07月-18日)</t>
+(21年-07月-19日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -35388,7 +35388,7 @@
           <t>E | 301呎 (1房)
 $764万
 $25,378/呎
-(21年-06月-02日)</t>
+(21年-06月-03日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -35396,7 +35396,7 @@
           <t>F | 299呎 (1房)
 $780万
 $26,101/呎
-(21年-05月-08日)</t>
+(21年-05月-09日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -35404,7 +35404,7 @@
           <t>G | 207呎 (开放式)
 $587万
 $28,378/呎
-(21年-09月-05日)</t>
+(21年-09月-06日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -35412,7 +35412,7 @@
           <t>H | 321呎 (1房)
 $857万
 $26,710/呎
-(21年-07月-19日)</t>
+(21年-07月-20日)</t>
         </is>
       </c>
     </row>
@@ -35430,7 +35430,7 @@
           <t>D | 309呎 (1房)
 $908万
 $29,385/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -35438,7 +35438,7 @@
           <t>E | 280呎 (1房)
 $848万
 $30,286/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -35446,7 +35446,7 @@
           <t>F | 277呎 (1房)
 $803万
 $29,000/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -35462,7 +35462,7 @@
           <t>H | 300呎 (1房)
 $918万
 $30,600/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
+++ b/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
@@ -9902,34 +9902,34 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
-        <v>19016000</v>
+        <v>18350400</v>
       </c>
       <c r="I150" s="5" t="n">
-        <v>34575</v>
+        <v>33364</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K150" s="5" t="n">
-        <v>17662200</v>
+        <v>18350400</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>32113</v>
+        <v>33364</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N150" s="3" t="inlineStr">
@@ -30545,7 +30545,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30555,7 +30555,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>222</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -31886,12 +31886,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 550呎 (2房)
-$1902万
-$34,575/呎
-(在售)</t>
+$1835万
+$33,364/呎
+(26年-08月-03日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">

--- a/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
+++ b/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
@@ -9406,7 +9406,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -15048,34 +15048,34 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
-        <v>29338000</v>
+        <v>28311100</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>33001</v>
+        <v>31846</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K233" s="5" t="n">
-        <v>27107800</v>
+        <v>28311100</v>
       </c>
       <c r="L233" s="5" t="n">
-        <v>30492</v>
+        <v>31846</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -15544,7 +15544,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -15606,7 +15606,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -15978,7 +15978,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -16102,7 +16102,7 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -17652,7 +17652,7 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -17838,7 +17838,7 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -18396,7 +18396,7 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -28188,7 +28188,7 @@
         </is>
       </c>
       <c r="E445" s="4" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F445" s="3" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>8547800</v>
       </c>
       <c r="I445" s="5" t="n">
-        <v>26629</v>
+        <v>26546</v>
       </c>
       <c r="J445" s="3" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>8547800</v>
       </c>
       <c r="L445" s="5" t="n">
-        <v>26629</v>
+        <v>26546</v>
       </c>
       <c r="M445" s="3" t="inlineStr">
         <is>
@@ -30545,22 +30545,22 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -31799,12 +31799,12 @@
 (21年-05月-31日)</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 550呎 (2房)
 $1926万
 $35,018/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -31878,12 +31878,12 @@
 (21年-10月-06日)</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 550呎 (2房)
 $1920万
 $34,915/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -31957,12 +31957,12 @@
 (26年-02月-27日)</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 550呎 (2房)
 $1915万
 $34,811/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -32281,12 +32281,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D26" s="24" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 550呎 (2房)
 $1879万
 $34,162/呎
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -32360,12 +32360,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D27" s="24" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 550呎 (2房)
 $1873万
 $34,060/呎
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -32439,12 +32439,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 550呎 (2房)
 $1868万
 $33,956/呎
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -32526,12 +32526,12 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E29" s="24" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 546呎 (2房)
 $183750001865万
 $3,365,384,649,544/呎
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -32581,12 +32581,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 889呎 (3房)
-$2934万
-$33,001/呎
-(在售)</t>
+$2831万
+$31,846/呎
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -32660,28 +32660,28 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B31" s="24" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>A | 889呎 (3房)
 $279630002866万
 $3,145,444,351,701/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C31" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 550呎 (2房)
 $1846万
 $33,564/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D31" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 550呎 (2房)
 $1828万
 $33,236/呎
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -32739,36 +32739,36 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B32" s="24" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>A | 889呎 (3房)
 $279600002866万
 $3,145,106,893,880/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C32" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>B | 550呎 (2房)
 $1846万
 $33,564/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D32" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>C | 550呎 (2房)
 $1828万
 $33,236/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E32" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>D | 546呎 (2房)
 $180360001831万
 $3,303,296,736,826/呎
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -32897,12 +32897,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B34" s="23" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>A | 889呎 (3房)
 $2850万
 $32,057/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
@@ -32921,12 +32921,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>D | 546呎 (2房)
 $1783万
 $32,661/呎
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -32976,12 +32976,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>A | 889呎 (3房)
 $2841万
 $31,956/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C35" s="23" t="inlineStr">
@@ -33000,12 +33000,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>D | 546呎 (2房)
 $1778万
 $32,557/呎
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -33055,12 +33055,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B36" s="23" t="inlineStr">
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>A | 889呎 (3房)
 $2823万
 $31,757/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C36" s="23" t="inlineStr">
@@ -33079,12 +33079,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>D | 546呎 (2房)
 $1766万
 $32,352/呎
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
@@ -35196,9 +35196,9 @@
       </c>
       <c r="I6" s="20" t="inlineStr">
         <is>
-          <t>H | 321呎 (1房)
+          <t>H | 322呎 (1房)
 $855万
-$26,629/呎
+$26,546/呎
 (21年-05月-31日)</t>
         </is>
       </c>

--- a/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
+++ b/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
@@ -9907,7 +9907,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -31891,7 +31891,7 @@
           <t>C | 550呎 (2房)
 $1835万
 $33,364/呎
-(26年-08月-03日)</t>
+(26年-08月-26日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">

--- a/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
+++ b/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
@@ -19570,7 +19570,7 @@
         </is>
       </c>
       <c r="E306" s="4" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>8783700</v>
       </c>
       <c r="I306" s="5" t="n">
-        <v>26537</v>
+        <v>26617</v>
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>8783700</v>
       </c>
       <c r="L306" s="5" t="n">
-        <v>26537</v>
+        <v>26617</v>
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
@@ -33437,9 +33437,9 @@
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>D | 331呎 (1房)
+          <t>D | 330呎 (1房)
 $878万
-$26,537/呎
+$26,617/呎
 (21年-06月-30日)</t>
         </is>
       </c>

--- a/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
+++ b/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
@@ -15044,7 +15044,7 @@
         </is>
       </c>
       <c r="E233" s="4" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>28311100</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>31846</v>
+        <v>31810</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>28311100</v>
       </c>
       <c r="L233" s="5" t="n">
-        <v>31846</v>
+        <v>31810</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
@@ -32583,9 +32583,9 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>A | 889呎 (3房)
+          <t>A | 890呎 (3房)
 $2831万
-$31,846/呎
+$31,810/呎
 (26年-08月-18日)</t>
         </is>
       </c>
